--- a/jpcore-r4/feature/fix-tx-error/CodeSystem-jp-condition-disease-outcome-jhsd0006-cs.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/CodeSystem-jp-condition-disease-outcome-jhsd0006-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright Japanese  Association of Healthcare Information Systems Industry(JAHIS)  一般社団法人保健医療福祉情報システム工業会</t>
+    <t>Copyright Japanese Association of Healthcare Information Systems Industry(JAHIS)  一般社団法人保健医療福祉情報システム工業会</t>
   </si>
   <si>
     <t>Case Sensitive</t>
